--- a/Configs/Datas/__beans__.xlsx
+++ b/Configs/Datas/__beans__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52892A95-BBDD-42B6-A9C8-E869A5FA9CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0269E44-B3B0-4C8B-965E-64776CC1508A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -92,6 +92,151 @@
   </si>
   <si>
     <t>字段变体</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.CostInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>,</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能消耗配置</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.AttributeId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Require</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cost</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.HitEffectData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>Param1</t>
+  </si>
+  <si>
+    <t>Param2</t>
+  </si>
+  <si>
+    <t>Param3</t>
+  </si>
+  <si>
+    <t>ZZZ.HitEffectType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.EffectTarget</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果类型</t>
+  </si>
+  <si>
+    <t>作用目标</t>
+  </si>
+  <si>
+    <t>触发策略</t>
+  </si>
+  <si>
+    <t>参数2 (喧响值 / 备用)</t>
+  </si>
+  <si>
+    <t>参数3 (目标AttributeId / 要挂的BuffId)</t>
+  </si>
+  <si>
+    <t>技能命中效果配置</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF292929"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>参数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF292929"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF292929"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>属性变化量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF292929"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.EffectTriggerPolicy</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -99,7 +244,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,6 +280,26 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF292929"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF292929"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF292929"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -177,7 +342,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -185,6 +350,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
@@ -467,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="20.625" customWidth="1"/>
@@ -505,15 +676,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -568,6 +739,123 @@
       </c>
       <c r="P3" s="2" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="J10" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J11" t="s">
+        <v>39</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J12" t="s">
+        <v>40</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/__beans__.xlsx
+++ b/Configs/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0269E44-B3B0-4C8B-965E-64776CC1508A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49982B73-487C-4B41-89D2-D7E0E7E80D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="72">
   <si>
     <t>##var</t>
   </si>
@@ -95,72 +95,22 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>ZZZ.CostInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>,</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>技能消耗配置</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Type</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>ZZZ.AttributeId</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>资源类型</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Require</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cost</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>需求量</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗量</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>ZZZ.HitEffectData</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>Policy</t>
-  </si>
-  <si>
-    <t>Param1</t>
-  </si>
-  <si>
-    <t>Param2</t>
-  </si>
-  <si>
-    <t>Param3</t>
-  </si>
-  <si>
     <t>ZZZ.HitEffectType</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -176,68 +126,139 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>效果类型</t>
-  </si>
-  <si>
-    <t>作用目标</t>
-  </si>
-  <si>
-    <t>触发策略</t>
-  </si>
-  <si>
-    <t>参数2 (喧响值 / 备用)</t>
-  </si>
-  <si>
-    <t>参数3 (目标AttributeId / 要挂的BuffId)</t>
-  </si>
-  <si>
     <t>技能命中效果配置</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF292929"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>参数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF292929"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>1 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF292929"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>属性变化量</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF292929"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>ZZZ.EffectTriggerPolicy</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.CustomAttrCfg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色独有/扩展属性初始定义</t>
+  </si>
+  <si>
+    <t>属性枚举 ID</t>
+  </si>
+  <si>
+    <t>attr_id</t>
+  </si>
+  <si>
+    <t>init_val</t>
+  </si>
+  <si>
+    <t>max_val</t>
+  </si>
+  <si>
+    <t>min_val</t>
+  </si>
+  <si>
+    <t>初始值</t>
+  </si>
+  <si>
+    <t>最大值上限</t>
+  </si>
+  <si>
+    <t>最小值下限</t>
+  </si>
+  <si>
+    <t>attr_id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.AttributeCondition</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用属性条件校验</t>
+  </si>
+  <si>
+    <t>op</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>校验的属性 ID</t>
+  </si>
+  <si>
+    <t>比较运算符 (如 GreaterEqual)</t>
+  </si>
+  <si>
+    <t>要求的对比目标值</t>
+  </si>
+  <si>
+    <t>ZZZ.CompareOp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.CostType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.AttributeCost</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用属性扣减消耗</t>
+  </si>
+  <si>
+    <t>cost_type</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>扣减的属性 ID</t>
+  </si>
+  <si>
+    <t>扣减类型</t>
+  </si>
+  <si>
+    <t>扣减数量</t>
+  </si>
+  <si>
+    <t>effect_target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>trigger_policy</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect_type</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff_id</t>
+  </si>
+  <si>
+    <t>chance</t>
+  </si>
+  <si>
+    <t>命中效果类型（Damage / ModifyAttribute / ApplyBuff）</t>
+  </si>
+  <si>
+    <t>作用目标（Victim 受击者 / Attacker 攻击者自身）</t>
+  </si>
+  <si>
+    <t>多段打击触发策略（EveryHit 每段 / FirstHitOnly 仅首段 / LastHitOnly 仅末段）</t>
+  </si>
+  <si>
+    <t>目标属性 ID（仅在 ModifyAttribute 时生效，如 TeamDecibel, Ellen_FlashFreeze；其他填 None）</t>
+  </si>
+  <si>
+    <t>数值(正):Damage 时：表示伤害基础倍率/系数（如 1.5 表示 150% 倍率），ModifyAttribute 时：表示获得的属性增量（如 15 表示获得 15 点喧响）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff ID（仅在 ApplyBuff 时生效，无则填 0）</t>
+  </si>
+  <si>
+    <t>触发概率（0.0 ~ 1.0，默认 1.0 表示 100% 触发）</t>
   </si>
 </sst>
 </file>
@@ -342,7 +363,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -360,6 +381,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -638,14 +662,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="4" width="20.625" customWidth="1"/>
+    <col min="2" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="4.125" customWidth="1"/>
+    <col min="4" max="4" width="4.375" customWidth="1"/>
     <col min="5" max="6" width="12.25" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="12" width="13.5" customWidth="1"/>
+    <col min="10" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="19" customWidth="1"/>
     <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col min="14" max="14" width="42.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
@@ -743,119 +771,225 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>28</v>
+      <c r="N4" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J5" s="2" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J6" s="2" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="J7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J7" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="N7" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J8" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>46</v>
+        <v>29</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J9" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J10" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>51</v>
+        <v>29</v>
+      </c>
+      <c r="N10" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="J11" t="s">
-        <v>39</v>
+      <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>48</v>
+        <v>24</v>
+      </c>
+      <c r="N11" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N12" t="s">
         <v>40</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N12" s="3" t="s">
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J14" t="s">
+        <v>39</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J16" t="s">
+        <v>46</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J17" t="s">
+        <v>47</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" t="s">
+        <v>54</v>
+      </c>
+      <c r="J18" t="s">
+        <v>36</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J19" t="s">
+        <v>55</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J20" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N20" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/__beans__.xlsx
+++ b/Configs/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49982B73-487C-4B41-89D2-D7E0E7E80D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B41DDCE-3E39-4AFF-898F-2CFDECD39268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="75">
   <si>
     <t>##var</t>
   </si>
@@ -259,13 +259,34 @@
   </si>
   <si>
     <t>触发概率（0.0 ~ 1.0，默认 1.0 表示 100% 触发）</t>
+  </si>
+  <si>
+    <t>hit_reaction</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.HitReactionType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF292929"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>受击反馈类型</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,6 +341,13 @@
       <color rgb="FF292929"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF292929"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -379,11 +407,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -662,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.625" customWidth="1"/>
@@ -704,15 +732,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -829,7 +857,7 @@
       <c r="L8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="5" t="s">
         <v>69</v>
       </c>
     </row>
@@ -856,139 +884,150 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B11" s="2" t="s">
+      <c r="J11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G12" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N11" t="s">
+      <c r="N12" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="J12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N12" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="N13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="N14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J15" t="s">
+        <v>39</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B15" s="2" t="s">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G16" t="s">
         <v>45</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J16" t="s">
         <v>36</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N15" t="s">
+      <c r="N16" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="J16" t="s">
-        <v>46</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N16" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
       <c r="J17" t="s">
+        <v>46</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J18" t="s">
         <v>47</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="L18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="N17" t="s">
+      <c r="N18" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B18" s="2" t="s">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G19" t="s">
         <v>54</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J19" t="s">
         <v>36</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="L19" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N18" t="s">
+      <c r="N19" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="J19" t="s">
-        <v>55</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="N19" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
       <c r="J20" t="s">
+        <v>55</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="J21" t="s">
         <v>56</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="L21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="N20" t="s">
+      <c r="N21" t="s">
         <v>59</v>
       </c>
     </row>

--- a/Configs/Datas/__beans__.xlsx
+++ b/Configs/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B41DDCE-3E39-4AFF-898F-2CFDECD39268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B9DB6F-C76D-41E3-A0F9-379FDD5B7A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -269,16 +269,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF292929"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>受击反馈类型</t>
-    </r>
+    <t>受击反馈类型</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -344,11 +335,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FF292929"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -391,7 +383,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -412,6 +404,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -890,7 +885,7 @@
       <c r="L11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1037,6 +1032,6 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>